--- a/Result/profitability/4728.xlsx
+++ b/Result/profitability/4728.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM69"/>
+  <dimension ref="A1:AM70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.35</v>
       </c>
       <c r="M2" t="n">
-        <v>2.86625</v>
+        <v>3.02875</v>
       </c>
       <c r="N2" t="n">
-        <v>75.22874999999999</v>
+        <v>75.535</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>-0.57</v>
       </c>
       <c r="M3" t="n">
-        <v>2.40125</v>
+        <v>2.615</v>
       </c>
       <c r="N3" t="n">
-        <v>72.38250000000001</v>
+        <v>72.64625000000001</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>-0.39</v>
       </c>
       <c r="M4" t="n">
-        <v>2.01</v>
+        <v>2.05375</v>
       </c>
       <c r="N4" t="n">
-        <v>62.62625</v>
+        <v>62.91625</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>0.13</v>
       </c>
       <c r="M5" t="n">
-        <v>1.51375</v>
+        <v>1.715</v>
       </c>
       <c r="N5" t="n">
-        <v>62.05125</v>
+        <v>62.39625</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.55</v>
       </c>
       <c r="M6" t="n">
-        <v>1.2275</v>
+        <v>1.34875</v>
       </c>
       <c r="N6" t="n">
-        <v>62.48625</v>
+        <v>62.98375</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-0.16</v>
       </c>
       <c r="M7" t="n">
-        <v>0.7725</v>
+        <v>0.9662500000000001</v>
       </c>
       <c r="N7" t="n">
-        <v>58.21375</v>
+        <v>58.81875</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.22</v>
       </c>
       <c r="M8" t="n">
-        <v>0.4375000000000001</v>
+        <v>0.485</v>
       </c>
       <c r="N8" t="n">
-        <v>56.76375</v>
+        <v>57.13375</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -9191,6 +9191,133 @@
       </c>
       <c r="AM69" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>4728</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>618</v>
+      </c>
+      <c r="D70" t="n">
+        <v>112</v>
+      </c>
+      <c r="E70" t="n">
+        <v>506</v>
+      </c>
+      <c r="F70" t="n">
+        <v>81.87</v>
+      </c>
+      <c r="G70" t="n">
+        <v>329</v>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>53.26%</t>
+        </is>
+      </c>
+      <c r="I70" t="n">
+        <v>3</v>
+      </c>
+      <c r="J70" t="n">
+        <v>333</v>
+      </c>
+      <c r="K70" t="n">
+        <v>242</v>
+      </c>
+      <c r="L70" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="M70" t="n">
+        <v>3.46625</v>
+      </c>
+      <c r="N70" t="n">
+        <v>79.1925</v>
+      </c>
+      <c r="O70" t="n">
+        <v>1</v>
+      </c>
+      <c r="P70" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>1</v>
+      </c>
+      <c r="R70" t="n">
+        <v>1</v>
+      </c>
+      <c r="S70" t="n">
+        <v>1</v>
+      </c>
+      <c r="T70" t="n">
+        <v>1</v>
+      </c>
+      <c r="U70" t="n">
+        <v>1</v>
+      </c>
+      <c r="V70" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W70" t="n">
+        <v>0.3799999999999999</v>
+      </c>
+      <c r="X70" t="n">
+        <v>0.09336609336609336</v>
+      </c>
+      <c r="Y70" t="n">
+        <v>2.960000000000008</v>
+      </c>
+      <c r="Z70" t="n">
+        <v>0.03751108858192898</v>
+      </c>
+      <c r="AA70" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AB70" t="n">
+        <v>0.5669014084507045</v>
+      </c>
+      <c r="AC70" t="n">
+        <v>2.760000000000005</v>
+      </c>
+      <c r="AD70" t="n">
+        <v>0.03488813045127048</v>
+      </c>
+      <c r="AE70" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF70" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG70" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH70" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI70" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ70" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK70" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL70" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM70" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
